--- a/testing/test.xlsx
+++ b/testing/test.xlsx
@@ -424,9 +424,6 @@
       <c r="H1" t="str">
         <v>Supplier Name</v>
       </c>
-      <c r="I1" t="str">
-        <v>Custom Logo Size_x000d_</v>
-      </c>
       <c r="J1" t="str">
         <v/>
       </c>
@@ -478,32 +475,29 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>41432A5282</v>
+        <v>41432A5279</v>
       </c>
       <c r="B2" t="str">
-        <v>CT89240105</v>
+        <v>96000</v>
       </c>
       <c r="C2" t="str">
-        <v>Carhartt Brown</v>
+        <v>Blacktop</v>
       </c>
       <c r="D2" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845693</v>
       </c>
       <c r="E2" t="str">
-        <v>White</v>
+        <v xml:space="preserve">Black </v>
       </c>
       <c r="F2" t="str">
-        <v>BAG-FRONT</v>
+        <v>BAG-ON-POCKET</v>
       </c>
       <c r="G2" t="str">
-        <v>L152FNavy-10036294_11952739-72-8-9jpg</v>
+        <v>EB510FCobaltBlue-10036294_11952739-57-8-9.jpg</v>
       </c>
       <c r="H2" t="str">
         <v>SanMar</v>
       </c>
-      <c r="I2" t="str">
-        <v>100x80_x000d_</v>
-      </c>
       <c r="J2" t="str">
         <v/>
       </c>
@@ -551,6 +545,9 @@
       </c>
       <c r="Y2" t="str">
         <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v>_x000d_</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +558,7 @@
         <v>96000</v>
       </c>
       <c r="C3" t="str">
-        <v>SignalRed</v>
+        <v>Tarmac Grey Heather</v>
       </c>
       <c r="D3" t="str">
         <v>9953285_11845694</v>
@@ -570,17 +567,14 @@
         <v>White</v>
       </c>
       <c r="F3" t="str">
-        <v>BAG-FRONT</v>
+        <v>ON BAG POCKET</v>
       </c>
       <c r="G3" t="str">
-        <v>CSV40FNavy-10036294_11952742-16-8-9.jpg</v>
+        <v>EB510FDeepBlack-10036294_11952739-57-8-9.jpg</v>
       </c>
       <c r="H3" t="str">
         <v>SanMar</v>
       </c>
-      <c r="I3" t="str">
-        <v>100x80_x000d_</v>
-      </c>
       <c r="J3" t="str">
         <v/>
       </c>
@@ -634,7 +628,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
         <v/>
       </c>
     </row>

--- a/testing/test.xlsx
+++ b/testing/test.xlsx
@@ -1,41 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akshat Mittal\Desktop\photoshopAutomation\testing\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B61B07E-A68A-4218-A058-F29D245FDFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="24">
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Supplier Part ID</t>
+  </si>
+  <si>
+    <t>Supplier Color</t>
+  </si>
+  <si>
+    <t>Decoration Code</t>
+  </si>
+  <si>
+    <t>Decoration Color</t>
+  </si>
+  <si>
+    <t>Decoration Location</t>
+  </si>
+  <si>
+    <t>Final Image Name</t>
+  </si>
+  <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>41432A5279</t>
+  </si>
+  <si>
+    <t>96000</t>
+  </si>
+  <si>
+    <t>Blacktop</t>
+  </si>
+  <si>
+    <t>9953285_11845693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black </t>
+  </si>
+  <si>
+    <t>BAG-ON-POCKET</t>
+  </si>
+  <si>
+    <t>EB510FCobaltBlue-10036294_11952739-57-8-9.jpg</t>
+  </si>
+  <si>
+    <t>SanMar</t>
+  </si>
+  <si>
+    <t>_x000D_</t>
+  </si>
+  <si>
+    <t>Tarmac Grey Heather</t>
+  </si>
+  <si>
+    <t>9953285_11845694</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>ON BAG POCKET</t>
+  </si>
+  <si>
+    <t>EB510FDeepBlack-10036294_11952739-57-8-9.jpg</t>
+  </si>
+  <si>
+    <t>Custom Logo Size</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +128,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,290 +467,304 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Product ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Supplier Part ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Supplier Color</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Decoration Code</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Decoration Color</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Decoration Location</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Final Image Name</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Supplier Name</v>
-      </c>
-      <c r="J1" t="str">
-        <v/>
-      </c>
-      <c r="K1" t="str">
-        <v/>
-      </c>
-      <c r="L1" t="str">
-        <v/>
-      </c>
-      <c r="M1" t="str">
-        <v/>
-      </c>
-      <c r="N1" t="str">
-        <v/>
-      </c>
-      <c r="O1" t="str">
-        <v/>
-      </c>
-      <c r="P1" t="str">
-        <v/>
-      </c>
-      <c r="Q1" t="str">
-        <v/>
-      </c>
-      <c r="R1" t="str">
-        <v/>
-      </c>
-      <c r="S1" t="str">
-        <v/>
-      </c>
-      <c r="T1" t="str">
-        <v/>
-      </c>
-      <c r="U1" t="str">
-        <v/>
-      </c>
-      <c r="V1" t="str">
-        <v/>
-      </c>
-      <c r="W1" t="str">
-        <v/>
-      </c>
-      <c r="X1" t="str">
-        <v/>
-      </c>
-      <c r="Y1" t="str">
-        <v/>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" t="s">
+        <v>8</v>
+      </c>
+      <c r="U1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W1" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>41432A5279</v>
-      </c>
-      <c r="B2" t="str">
-        <v>96000</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Blacktop</v>
-      </c>
-      <c r="D2" t="str">
-        <v>9953285_11845693</v>
-      </c>
-      <c r="E2" t="str">
-        <v xml:space="preserve">Black </v>
-      </c>
-      <c r="F2" t="str">
-        <v>BAG-ON-POCKET</v>
-      </c>
-      <c r="G2" t="str">
-        <v>EB510FCobaltBlue-10036294_11952739-57-8-9.jpg</v>
-      </c>
-      <c r="H2" t="str">
-        <v>SanMar</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v>_x000d_</v>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>120</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>41432A5279</v>
-      </c>
-      <c r="B3" t="str">
-        <v>96000</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Tarmac Grey Heather</v>
-      </c>
-      <c r="D3" t="str">
-        <v>9953285_11845694</v>
-      </c>
-      <c r="E3" t="str">
-        <v>White</v>
-      </c>
-      <c r="F3" t="str">
-        <v>ON BAG POCKET</v>
-      </c>
-      <c r="G3" t="str">
-        <v>EB510FDeepBlack-10036294_11952739-57-8-9.jpg</v>
-      </c>
-      <c r="H3" t="str">
-        <v>SanMar</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str">
-        <v/>
-      </c>
-      <c r="V3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>120</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <v/>
-      </c>
-      <c r="X4" t="str">
-        <v/>
-      </c>
-      <c r="Y4" t="str">
-        <v/>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" t="s">
+        <v>8</v>
+      </c>
+      <c r="U4" t="s">
+        <v>8</v>
+      </c>
+      <c r="V4" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" t="s">
+        <v>8</v>
+      </c>
+      <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z4"/>
+    <ignoredError sqref="A4:Z4 A1:H1 J1:Z1 A2:H2 J2:Z2 A3:H3 J3:Z3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>